--- a/data/trans_orig/Q64A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva trabajando en su empresa (en meses)</t>
+          <t>Tiempo medio que lleva trabajando en su empresa (en meses) (tasa de respuesta: 97,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 110,62</t>
+          <t>79,59; 110,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101,88; 146,43</t>
+          <t>101,92; 146,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,48; 139,01</t>
+          <t>97,75; 143,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131,06; 170,74</t>
+          <t>131,29; 169,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,7; 71,33</t>
+          <t>40,02; 68,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,52; 119,29</t>
+          <t>78,8; 119,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,07; 129,49</t>
+          <t>93,41; 132,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>106,98; 131,34</t>
+          <t>105,68; 131,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,57; 90,42</t>
+          <t>67,49; 89,47</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,7; 128,88</t>
+          <t>97,34; 129,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100,93; 130,9</t>
+          <t>100,55; 130,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>126,05; 148,69</t>
+          <t>125,35; 149,37</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>99,46; 126,99</t>
+          <t>99,81; 127,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115,48; 157,46</t>
+          <t>115,5; 156,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,7; 122,24</t>
+          <t>91,08; 121,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116,37; 158,54</t>
+          <t>116,78; 158,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,31; 85,48</t>
+          <t>54,16; 85,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,97; 106,71</t>
+          <t>69,39; 109,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,57; 102,72</t>
+          <t>69,5; 103,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>99,19; 130,71</t>
+          <t>98,71; 128,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,32; 108,9</t>
+          <t>88,11; 110,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100,38; 130,52</t>
+          <t>100,8; 130,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85,63; 109,14</t>
+          <t>85,58; 109,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>113,8; 142,43</t>
+          <t>112,8; 141,35</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>106,54; 136,96</t>
+          <t>107,18; 135,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>103,92; 140,03</t>
+          <t>102,26; 141,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105,43; 139,23</t>
+          <t>104,13; 138,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128,83; 170,87</t>
+          <t>127,63; 170,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>70,57; 110,1</t>
+          <t>68,24; 110,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,87; 90,09</t>
+          <t>57,59; 89,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,29; 118,75</t>
+          <t>69,66; 116,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,18; 124,93</t>
+          <t>91,65; 126,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,35; 121,96</t>
+          <t>97,45; 122,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89,3; 118,35</t>
+          <t>91,02; 118,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94,58; 124,88</t>
+          <t>96,07; 123,73</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116,9; 145,49</t>
+          <t>116,19; 145,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>106,3; 136,83</t>
+          <t>106,84; 135,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>108,96; 148,63</t>
+          <t>109,23; 149,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120,71; 175,63</t>
+          <t>119,75; 173,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129,82; 191,37</t>
+          <t>128,92; 185,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>60,07; 86,46</t>
+          <t>58,51; 86,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,57; 123,56</t>
+          <t>83,69; 127,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,1; 143,48</t>
+          <t>89,38; 141,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,08; 140,19</t>
+          <t>59,03; 140,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,83; 113,02</t>
+          <t>91,79; 113,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102,8; 133,86</t>
+          <t>102,56; 130,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114,02; 152,77</t>
+          <t>114,72; 154,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,7; 152,47</t>
+          <t>84,38; 152,67</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,69; 113,09</t>
+          <t>72,05; 110,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>94,88; 147,19</t>
+          <t>96,26; 148,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>87,17; 131,58</t>
+          <t>88,84; 134,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>126,61; 162,69</t>
+          <t>127,7; 161,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,29; 80,68</t>
+          <t>37,21; 79,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,92; 138,59</t>
+          <t>79,33; 135,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,23; 116,94</t>
+          <t>61,99; 114,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>103,41; 129,02</t>
+          <t>105,93; 131,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,4; 94,1</t>
+          <t>63,82; 95,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93,05; 132,56</t>
+          <t>97,47; 137,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85,44; 120,41</t>
+          <t>83,48; 118,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>120,63; 140,84</t>
+          <t>120,24; 141,46</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>96,43; 127,26</t>
+          <t>97,15; 128,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131,36; 185,44</t>
+          <t>131,66; 187,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134,67; 180,63</t>
+          <t>133,94; 180,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>142,03; 185,44</t>
+          <t>141,82; 183,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,1; 78,58</t>
+          <t>46,38; 80,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>60,35; 106,01</t>
+          <t>61,22; 105,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>96,76; 145,48</t>
+          <t>95,45; 143,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>123,55; 175,06</t>
+          <t>123,11; 168,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,17; 106,62</t>
+          <t>82,17; 106,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113,78; 155,4</t>
+          <t>113,82; 156,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125,19; 158,51</t>
+          <t>125,28; 157,72</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141,81; 171,97</t>
+          <t>141,92; 171,94</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>89,8; 110,9</t>
+          <t>87,48; 111,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>116,37; 144,76</t>
+          <t>116,78; 143,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,85; 112,16</t>
+          <t>88,32; 112,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117,56; 147,15</t>
+          <t>116,94; 146,49</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,64; 83,85</t>
+          <t>57,02; 84,52</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,55; 104,96</t>
+          <t>73,79; 104,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,03; 86,89</t>
+          <t>65,11; 86,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>101,52; 123,26</t>
+          <t>101,36; 123,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,72; 98,81</t>
+          <t>80,85; 97,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>103,49; 124,67</t>
+          <t>102,56; 123,98</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,54; 97,13</t>
+          <t>80,83; 97,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>114,09; 133,57</t>
+          <t>113,72; 132,46</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>88,69; 109,73</t>
+          <t>89,2; 109,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>102,21; 124,63</t>
+          <t>101,1; 124,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107,93; 132,42</t>
+          <t>107,58; 131,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29,29; 143,37</t>
+          <t>32,58; 144,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>81,55; 107,42</t>
+          <t>79,99; 106,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,07; 91,93</t>
+          <t>68,23; 91,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,32; 104,2</t>
+          <t>80,66; 104,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>100,59; 122,94</t>
+          <t>101,07; 124,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>89,11; 105,11</t>
+          <t>88,59; 104,66</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90,77; 107,88</t>
+          <t>90,84; 106,98</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99,77; 117,69</t>
+          <t>99,54; 117,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>43,59; 130,63</t>
+          <t>44,8; 131,62</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100,34; 109,91</t>
+          <t>100,63; 110,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120,03; 132,41</t>
+          <t>120,49; 133,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110,99; 123,09</t>
+          <t>110,9; 122,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>76,02; 145,69</t>
+          <t>81,66; 145,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,85; 78,58</t>
+          <t>67,59; 78,73</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,29; 92,92</t>
+          <t>80,36; 93,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,53; 97,52</t>
+          <t>85,62; 97,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>98,68; 119,31</t>
+          <t>98,67; 119,3</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90,5; 98,07</t>
+          <t>90,55; 98,13</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105,29; 114,85</t>
+          <t>105,55; 114,71</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102,3; 111,09</t>
+          <t>102,04; 110,7</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>85,53; 131,89</t>
+          <t>83,53; 131,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151,1</t>
+          <t>142,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>118,89</t>
+          <t>113,68</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>137,52</t>
+          <t>130,09</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>79,59; 110,91</t>
+          <t>79,99; 111,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>101,92; 146,61</t>
+          <t>101,06; 144,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,75; 143,35</t>
+          <t>97,73; 140,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131,29; 169,21</t>
+          <t>125,4; 156,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,02; 68,68</t>
+          <t>39,87; 69,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,8; 119,05</t>
+          <t>76,34; 118,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,41; 132,76</t>
+          <t>93,23; 131,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>105,68; 131,26</t>
+          <t>103,4; 125,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,49; 89,47</t>
+          <t>65,87; 89,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,34; 129,93</t>
+          <t>95,52; 127,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100,55; 130,43</t>
+          <t>101,6; 130,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>125,35; 149,37</t>
+          <t>118,18; 140,24</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135,11</t>
+          <t>132,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>113,34</t>
+          <t>112,9</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>126,24</t>
+          <t>124,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>99,81; 127,45</t>
+          <t>98,82; 126,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>115,5; 156,85</t>
+          <t>116,35; 156,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>91,08; 121,37</t>
+          <t>92,0; 120,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116,78; 158,63</t>
+          <t>114,3; 155,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>54,16; 85,8</t>
+          <t>54,48; 87,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,39; 109,13</t>
+          <t>68,52; 107,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>69,5; 103,87</t>
+          <t>68,52; 102,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>98,71; 128,06</t>
+          <t>98,34; 129,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>88,11; 110,41</t>
+          <t>88,03; 109,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100,8; 130,25</t>
+          <t>100,06; 130,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85,58; 109,09</t>
+          <t>85,25; 108,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>112,8; 141,35</t>
+          <t>110,39; 136,19</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>148,64</t>
+          <t>146,74</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>107,06</t>
+          <t>106,9</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>129,92</t>
+          <t>128,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>107,18; 135,83</t>
+          <t>105,24; 135,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>102,26; 141,38</t>
+          <t>104,34; 141,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>104,13; 138,78</t>
+          <t>103,82; 139,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127,63; 170,67</t>
+          <t>127,34; 167,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>68,24; 110,35</t>
+          <t>69,78; 109,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>57,59; 89,79</t>
+          <t>57,22; 91,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,66; 116,56</t>
+          <t>70,71; 117,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,65; 126,68</t>
+          <t>90,75; 127,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>97,45; 122,51</t>
+          <t>97,81; 123,14</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,02; 118,81</t>
+          <t>90,49; 119,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>96,07; 123,73</t>
+          <t>95,42; 122,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>116,19; 145,3</t>
+          <t>115,51; 143,41</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156,74</t>
+          <t>141,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>98,22</t>
+          <t>125,77</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>123,62</t>
+          <t>134,55</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>106,84; 135,74</t>
+          <t>105,79; 136,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>109,23; 149,18</t>
+          <t>109,1; 148,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>119,75; 173,72</t>
+          <t>121,48; 176,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128,92; 185,56</t>
+          <t>117,55; 170,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>58,51; 86,81</t>
+          <t>59,14; 86,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,69; 127,61</t>
+          <t>83,18; 126,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,38; 141,31</t>
+          <t>90,72; 142,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>59,03; 140,97</t>
+          <t>104,13; 145,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>91,79; 113,8</t>
+          <t>91,79; 113,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102,56; 130,92</t>
+          <t>103,08; 134,3</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>114,72; 154,2</t>
+          <t>114,18; 153,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,38; 152,67</t>
+          <t>118,54; 152,43</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143,79</t>
+          <t>133,81</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>116,31</t>
+          <t>112,34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>130,22</t>
+          <t>123,59</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>72,05; 110,23</t>
+          <t>69,87; 111,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>96,26; 148,65</t>
+          <t>95,71; 149,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88,84; 134,75</t>
+          <t>87,16; 132,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127,7; 161,87</t>
+          <t>118,72; 152,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,21; 79,49</t>
+          <t>36,1; 76,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,33; 135,05</t>
+          <t>82,35; 139,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,99; 114,25</t>
+          <t>63,65; 116,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>105,93; 131,56</t>
+          <t>101,33; 125,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63,82; 95,09</t>
+          <t>62,88; 96,38</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97,47; 137,16</t>
+          <t>95,41; 136,09</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>83,48; 118,56</t>
+          <t>84,07; 117,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>120,24; 141,46</t>
+          <t>112,87; 133,54</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162,97</t>
+          <t>159,02</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>156,63</t>
+          <t>154,22</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>97,15; 128,83</t>
+          <t>96,8; 127,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>131,66; 187,22</t>
+          <t>131,65; 187,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>133,94; 180,03</t>
+          <t>136,44; 181,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141,82; 183,91</t>
+          <t>138,57; 179,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46,38; 80,03</t>
+          <t>44,22; 80,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61,22; 105,6</t>
+          <t>58,91; 105,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,45; 143,15</t>
+          <t>96,84; 145,03</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>123,11; 168,96</t>
+          <t>122,78; 169,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>82,17; 106,9</t>
+          <t>82,29; 107,43</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>113,82; 156,89</t>
+          <t>113,45; 155,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>125,28; 157,72</t>
+          <t>125,32; 158,51</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>141,92; 171,94</t>
+          <t>137,32; 170,14</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>133,25</t>
+          <t>126,36</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>112,37</t>
+          <t>109,67</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>123,26</t>
+          <t>118,29</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,48; 111,47</t>
+          <t>89,69; 111,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>116,78; 143,87</t>
+          <t>115,73; 145,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88,32; 112,52</t>
+          <t>88,72; 111,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>116,94; 146,49</t>
+          <t>113,14; 140,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>57,02; 84,52</t>
+          <t>56,71; 83,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,79; 104,97</t>
+          <t>72,5; 103,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,11; 86,3</t>
+          <t>65,23; 85,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>101,36; 123,77</t>
+          <t>99,63; 119,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80,85; 97,58</t>
+          <t>80,01; 96,99</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102,56; 123,98</t>
+          <t>102,02; 123,86</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80,83; 97,42</t>
+          <t>80,55; 97,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>113,72; 132,46</t>
+          <t>110,47; 126,96</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>84,63</t>
+          <t>134,4</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>112,37</t>
+          <t>108,69</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>92,97</t>
+          <t>123,92</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>89,2; 109,3</t>
+          <t>88,86; 109,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>101,1; 124,08</t>
+          <t>102,42; 124,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>107,58; 131,99</t>
+          <t>107,4; 131,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,58; 144,53</t>
+          <t>123,09; 145,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>79,99; 106,67</t>
+          <t>80,19; 104,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>68,23; 91,54</t>
+          <t>68,6; 91,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>80,66; 104,92</t>
+          <t>80,43; 104,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>101,07; 124,71</t>
+          <t>99,02; 119,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,59; 104,66</t>
+          <t>88,16; 105,13</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>90,84; 106,98</t>
+          <t>90,28; 107,99</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99,54; 117,26</t>
+          <t>99,67; 117,17</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,8; 131,62</t>
+          <t>116,12; 131,78</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>125,25</t>
+          <t>136,69</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>113,16</t>
+          <t>114,09</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>120,19</t>
+          <t>126,8</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>100,63; 110,69</t>
+          <t>100,94; 110,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>120,49; 133,35</t>
+          <t>119,12; 132,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>110,9; 122,97</t>
+          <t>111,33; 123,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>81,66; 145,29</t>
+          <t>130,74; 142,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,59; 78,73</t>
+          <t>67,54; 78,61</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>80,36; 93,07</t>
+          <t>80,14; 92,21</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>85,62; 97,52</t>
+          <t>85,77; 97,87</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>98,67; 119,3</t>
+          <t>108,99; 119,15</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>90,55; 98,13</t>
+          <t>90,49; 98,06</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>105,55; 114,71</t>
+          <t>105,17; 114,86</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102,04; 110,7</t>
+          <t>101,7; 110,55</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>83,53; 131,26</t>
+          <t>122,73; 131,03</t>
         </is>
       </c>
     </row>
